--- a/Assets/Z_Level2/Z_DataSystem/Core/Form/Excels/Lab.xlsx
+++ b/Assets/Z_Level2/Z_DataSystem/Core/Form/Excels/Lab.xlsx
@@ -823,381 +823,254 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="15.625" customWidth="1"/>
-    <x:col min="2" max="2" width="29.600000381469727" customWidth="1"/>
-    <x:col min="3" max="3" width="20.5" customWidth="1"/>
-    <x:col min="4" max="4" width="20.200000762939453" customWidth="1"/>
-    <x:col min="5" max="5" width="37.70000076293945" customWidth="1"/>
-    <x:col min="6" max="6" width="12.699999809265137" customWidth="1"/>
-    <x:col min="7" max="7" width="18.375" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="str">
-        <x:v>write;index1;index2;index3</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="str">
-        <x:v>write;index2;index3</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>write;index3</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>write;index;index1;index2;index3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="B3" s="1"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B5" s="1"/>
-    </x:row>
-    <x:row r="6" ht="15.600000381469727" customHeight="1">
-      <x:c r="A6">
-        <x:v>10001</x:v>
-      </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6"/>
-      <x:c r="E6" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15.600000381469727" customHeight="1">
-      <x:c r="A7">
-        <x:v>10002</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7"/>
-      <x:c r="E7" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15.600000381469727" customHeight="1">
-      <x:c r="A8">
-        <x:v>10003</x:v>
-      </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8"/>
-      <x:c r="E8" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15.600000381469727" customHeight="1">
-      <x:c r="A9">
-        <x:v>10004</x:v>
-      </x:c>
-      <x:c r="B9" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9"/>
-      <x:c r="E9" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15.600000381469727" customHeight="1">
-      <x:c r="A10">
-        <x:v>10005</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10"/>
-      <x:c r="E10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15.600000381469727" customHeight="1">
-      <x:c r="A11">
-        <x:v>10006</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11"/>
-      <x:c r="E11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15.600000381469727" customHeight="1">
-      <x:c r="A12">
-        <x:v>10007</x:v>
-      </x:c>
-      <x:c r="B12" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12"/>
-      <x:c r="E12" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15.600000381469727" customHeight="1">
-      <x:c r="A13">
-        <x:v>10008</x:v>
-      </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13"/>
-      <x:c r="E13" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="15.600000381469727" customHeight="1">
-      <x:c r="A14">
-        <x:v>10009</x:v>
-      </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C14"/>
-      <x:c r="E14" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="15.600000381469727" customHeight="1">
-      <x:c r="A15">
-        <x:v>10010</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15"/>
-      <x:c r="E15" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="15.600000381469727" customHeight="1">
-      <x:c r="A16">
-        <x:v>10011</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C16"/>
-      <x:c r="E16" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="15.600000381469727" customHeight="1">
-      <x:c r="A17">
-        <x:v>10012</x:v>
-      </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C17"/>
-      <x:c r="E17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="15.600000381469727" customHeight="1">
-      <x:c r="A18">
-        <x:v>10013</x:v>
-      </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C18"/>
-      <x:c r="E18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="15.600000381469727" customHeight="1">
-      <x:c r="A19">
-        <x:v>10014</x:v>
-      </x:c>
-      <x:c r="B19" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C19"/>
-      <x:c r="E19" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="15.600000381469727" customHeight="1">
-      <x:c r="A20">
-        <x:v>10015</x:v>
-      </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20"/>
-      <x:c r="E20" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="15.600000381469727" customHeight="1">
-      <x:c r="A21">
-        <x:v>10016</x:v>
-      </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C21"/>
-      <x:c r="E21" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="15.600000381469727" customHeight="1">
-      <x:c r="A22">
-        <x:v>10017</x:v>
-      </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C22"/>
-      <x:c r="E22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="15.600000381469727" customHeight="1">
-      <x:c r="A23">
-        <x:v>10018</x:v>
-      </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C23"/>
-      <x:c r="E23" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="15.600000381469727" customHeight="1">
-      <x:c r="A24">
-        <x:v>10019</x:v>
-      </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C24"/>
-      <x:c r="E24" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="15.600000381469727" customHeight="1">
-      <x:c r="A25">
-        <x:v>10020</x:v>
-      </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C25"/>
-      <x:c r="E25" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="15.600000381469727" customHeight="1">
-      <x:c r="A26">
-        <x:v>10021</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C26"/>
-      <x:c r="E26" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="15.600000381469727" customHeight="1">
-      <x:c r="A27">
-        <x:v>10022</x:v>
-      </x:c>
-      <x:c r="B27" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C27"/>
-      <x:c r="E27" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="15.600000381469727" customHeight="1">
-      <x:c r="A28">
-        <x:v>10023</x:v>
-      </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C28"/>
-      <x:c r="E28" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="15.600000381469727" customHeight="1">
-      <x:c r="A29">
-        <x:v>10024</x:v>
-      </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C29"/>
-      <x:c r="E29" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="15.600000381469727" customHeight="1">
-      <x:c r="A30">
-        <x:v>10025</x:v>
-      </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C30"/>
-      <x:c r="E30" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="29.600000381469727" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="20.200000762939453" customWidth="1"/>
+    <col min="5" max="5" width="37.70000076293945" customWidth="1"/>
+    <col min="6" max="6" width="12.699999809265137" customWidth="1"/>
+    <col min="7" max="7" width="18.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>lv1Lab</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lv2Lab</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>lv3Lab</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>belong</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>write;medium</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v>write;index1;index2;index3</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v>write;index2;index3</v>
+      </c>
+      <c r="D2" t="str">
+        <v>write;index3</v>
+      </c>
+      <c r="E2" t="str">
+        <v>write;index;index1;index2;index3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" ht="15.600000381469727" customHeight="1">
+      <c r="A6"/>
+      <c r="B6" s="1"/>
+      <c r="C6"/>
+      <c r="E6"/>
+    </row>
+    <row r="7" ht="15.600000381469727" customHeight="1">
+      <c r="A7"/>
+      <c r="B7" s="1"/>
+      <c r="C7"/>
+      <c r="E7"/>
+    </row>
+    <row r="8" ht="15.600000381469727" customHeight="1">
+      <c r="A8"/>
+      <c r="B8" s="1"/>
+      <c r="C8"/>
+      <c r="E8"/>
+    </row>
+    <row r="9" ht="15.600000381469727" customHeight="1">
+      <c r="A9"/>
+      <c r="B9" s="1"/>
+      <c r="C9"/>
+      <c r="E9"/>
+    </row>
+    <row r="10" ht="15.600000381469727" customHeight="1">
+      <c r="A10"/>
+      <c r="B10" s="1"/>
+      <c r="C10"/>
+      <c r="E10"/>
+    </row>
+    <row r="11" ht="15.600000381469727" customHeight="1">
+      <c r="A11"/>
+      <c r="B11" s="1"/>
+      <c r="C11"/>
+      <c r="E11"/>
+    </row>
+    <row r="12" ht="15.600000381469727" customHeight="1">
+      <c r="A12"/>
+      <c r="B12" s="1"/>
+      <c r="C12"/>
+      <c r="E12"/>
+    </row>
+    <row r="13" ht="15.600000381469727" customHeight="1">
+      <c r="A13"/>
+      <c r="B13" s="1"/>
+      <c r="C13"/>
+      <c r="E13"/>
+    </row>
+    <row r="14" ht="15.600000381469727" customHeight="1">
+      <c r="A14"/>
+      <c r="B14" s="1"/>
+      <c r="C14"/>
+      <c r="E14"/>
+    </row>
+    <row r="15" ht="15.600000381469727" customHeight="1">
+      <c r="A15"/>
+      <c r="B15" s="1"/>
+      <c r="C15"/>
+      <c r="E15"/>
+    </row>
+    <row r="16" ht="15.600000381469727" customHeight="1">
+      <c r="A16"/>
+      <c r="B16" s="1"/>
+      <c r="C16"/>
+      <c r="E16"/>
+    </row>
+    <row r="17" ht="15.600000381469727" customHeight="1">
+      <c r="A17"/>
+      <c r="B17" s="1"/>
+      <c r="C17"/>
+      <c r="E17"/>
+    </row>
+    <row r="18" ht="15.600000381469727" customHeight="1">
+      <c r="A18"/>
+      <c r="B18" s="1"/>
+      <c r="C18"/>
+      <c r="E18"/>
+    </row>
+    <row r="19" ht="15.600000381469727" customHeight="1">
+      <c r="A19"/>
+      <c r="B19" s="1"/>
+      <c r="C19"/>
+      <c r="E19"/>
+    </row>
+    <row r="20" ht="15.600000381469727" customHeight="1">
+      <c r="A20"/>
+      <c r="B20" s="1"/>
+      <c r="C20"/>
+      <c r="E20"/>
+    </row>
+    <row r="21" ht="15.600000381469727" customHeight="1">
+      <c r="A21"/>
+      <c r="B21" s="1"/>
+      <c r="C21"/>
+      <c r="E21"/>
+    </row>
+    <row r="22" ht="15.600000381469727" customHeight="1">
+      <c r="A22"/>
+      <c r="B22" s="1"/>
+      <c r="C22"/>
+      <c r="E22"/>
+    </row>
+    <row r="23" ht="15.600000381469727" customHeight="1">
+      <c r="A23"/>
+      <c r="B23" s="1"/>
+      <c r="C23"/>
+      <c r="E23"/>
+    </row>
+    <row r="24" ht="15.600000381469727" customHeight="1">
+      <c r="A24"/>
+      <c r="B24" s="1"/>
+      <c r="C24"/>
+      <c r="E24"/>
+    </row>
+    <row r="25" ht="15.600000381469727" customHeight="1">
+      <c r="A25"/>
+      <c r="B25" s="1"/>
+      <c r="C25"/>
+      <c r="E25"/>
+    </row>
+    <row r="26" ht="15.600000381469727" customHeight="1">
+      <c r="A26"/>
+      <c r="B26" s="1"/>
+      <c r="C26"/>
+      <c r="E26"/>
+    </row>
+    <row r="27" ht="15.600000381469727" customHeight="1">
+      <c r="A27"/>
+      <c r="B27" s="1"/>
+      <c r="C27"/>
+      <c r="E27"/>
+    </row>
+    <row r="28" ht="15.600000381469727" customHeight="1">
+      <c r="A28"/>
+      <c r="B28" s="1"/>
+      <c r="C28"/>
+      <c r="E28"/>
+    </row>
+    <row r="29" ht="15.600000381469727" customHeight="1">
+      <c r="A29"/>
+      <c r="B29" s="1"/>
+      <c r="C29"/>
+      <c r="E29"/>
+    </row>
+    <row r="30" ht="15.600000381469727" customHeight="1">
+      <c r="A30"/>
+      <c r="B30" s="1"/>
+      <c r="C30"/>
+      <c r="E30"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
